--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487606_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487606_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.239100000000001</v>
+        <v>9.7789</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5705</v>
+        <v>7.5925</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6686</v>
+        <v>2.1864</v>
       </c>
       <c r="G2" t="n">
         <v>6.7754</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8497</v>
+        <v>-0.3098</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1508</v>
+        <v>-0.1287</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6989</v>
+        <v>-0.1811</v>
       </c>
       <c r="V2" t="n">
         <v>4.2836</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1421</v>
+        <v>5.7025</v>
       </c>
       <c r="E3" t="n">
-        <v>2.394</v>
+        <v>1.9355</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7481</v>
+        <v>3.7669</v>
       </c>
       <c r="G3" t="n">
         <v>3.119</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7993</v>
+        <v>1.3597</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0329</v>
+        <v>0.5745</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7663</v>
+        <v>0.7852</v>
       </c>
       <c r="V3" t="n">
         <v>1.2239</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6415</v>
+        <v>5.445</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6863</v>
+        <v>2.408</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9552</v>
+        <v>3.037</v>
       </c>
       <c r="G4" t="n">
         <v>4.3694</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2801</v>
+        <v>-0.4767</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0779</v>
+        <v>-0.3561</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2023</v>
+        <v>-0.1205</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8361</v>
+        <v>4.2571</v>
       </c>
       <c r="E5" t="n">
-        <v>2.815</v>
+        <v>2.9361</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0211</v>
+        <v>1.3209</v>
       </c>
       <c r="G5" t="n">
         <v>2.3726</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1516</v>
+        <v>0.5726</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1222</v>
+        <v>0.2434</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0294</v>
+        <v>0.3292</v>
       </c>
       <c r="V5" t="n">
         <v>1.506</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4374</v>
+        <v>3.1549</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0651</v>
+        <v>1.5646</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3722</v>
+        <v>1.5903</v>
       </c>
       <c r="G6" t="n">
         <v>0.3761</v>
@@ -922,13 +922,13 @@
         <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4493</v>
+        <v>0.1668</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7413</v>
+        <v>0.2408</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.292</v>
+        <v>-0.074</v>
       </c>
       <c r="V6" t="n">
         <v>1.8358</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5952</v>
+        <v>2.3647</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0278</v>
+        <v>1.0699</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5673</v>
+        <v>1.2948</v>
       </c>
       <c r="G7" t="n">
         <v>1.0094</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7216</v>
+        <v>1.4911</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4262</v>
+        <v>0.4682</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2955</v>
+        <v>1.0229</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3299</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5145</v>
+        <v>0.7835</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5867</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0432</v>
+        <v>1.3702</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1153</v>
@@ -1078,13 +1078,13 @@
         <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6299</v>
+        <v>-0.3609</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0471</v>
+        <v>-0.1052</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5828</v>
+        <v>-0.2557</v>
       </c>
       <c r="V8" t="n">
         <v>0.0955</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4393</v>
+        <v>0.6484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4507</v>
+        <v>0.5508</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0114</v>
+        <v>0.0977</v>
       </c>
       <c r="G9" t="n">
         <v>0.4878</v>
@@ -1156,13 +1156,13 @@
         <v>0.194</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2425</v>
+        <v>-0.0334</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>P. RODRIGUEZ RIVERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4358</v>
+        <v>0.478</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3375</v>
+        <v>0.1856</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0982</v>
+        <v>0.2924</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7388</v>
+        <v>0.8995</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.4408</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2375</v>
+        <v>1.3402</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7615</v>
+        <v>0.724</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7209</v>
+        <v>-0.6385</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>1.3625</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0227</v>
+        <v>0.1754</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2554</v>
+        <v>0.1977</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2781</v>
+        <v>-0.0223</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2732</v>
+        <v>-0.7035</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.424</v>
+        <v>-0.1041</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1508</v>
+        <v>-0.5994</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6119</v>
+        <v>0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ RIVERO</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4119</v>
+        <v>0.4541</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3648</v>
+        <v>0.4376</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0471</v>
+        <v>0.0165</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8995</v>
+        <v>0.7388</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4408</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3402</v>
+        <v>-0.2375</v>
       </c>
       <c r="J11" t="n">
-        <v>0.724</v>
+        <v>0.7615</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6385</v>
+        <v>0.7209</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3625</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1754</v>
+        <v>-0.0227</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1977</v>
+        <v>0.2554</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0223</v>
+        <v>-0.2781</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7696</v>
+        <v>-0.2549</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0751</v>
+        <v>-0.3239</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8447</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2821</v>
+        <v>-0.6119</v>
       </c>
       <c r="W11" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1737</v>
+        <v>-5.3367</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3613</v>
+        <v>-3.061</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8124</v>
+        <v>-2.2757</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7878</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6263</v>
+        <v>-0.7893</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5933</v>
+        <v>-0.293</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0329</v>
+        <v>-0.4963</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>26.5192</v>
+        <v>27.7304</v>
       </c>
       <c r="E13" t="n">
-        <v>13.8217</v>
+        <v>15.0329</v>
       </c>
       <c r="F13" t="n">
-        <v>12.6972</v>
+        <v>12.6974</v>
       </c>
       <c r="G13" t="n">
         <v>18.2449</v>
@@ -1438,7 +1438,7 @@
         <v>10.7926</v>
       </c>
       <c r="I13" t="n">
-        <v>7.452</v>
+        <v>7.451999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>12.505</v>
@@ -1468,13 +1468,13 @@
         <v>13.5823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5494999999999998</v>
+        <v>0.6617000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0771</v>
+        <v>0.1343</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5276000000000002</v>
+        <v>0.5274999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>4.9433</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7497</v>
+        <v>3.401</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5388</v>
+        <v>2.1384</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2109</v>
+        <v>1.2626</v>
       </c>
       <c r="G14" t="n">
         <v>0.6062</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6076</v>
+        <v>1.259</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7065</v>
+        <v>0.3061</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9011</v>
+        <v>0.9528</v>
       </c>
       <c r="V14" t="n">
         <v>2.1179</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>D. ROPERO MORA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9053</v>
+        <v>1.1478</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9316</v>
+        <v>0.435</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0264</v>
+        <v>0.7128</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2109</v>
+        <v>0.1168</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2529</v>
+        <v>0.3081</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4638</v>
+        <v>-0.1913</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3894</v>
+        <v>0.1224</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8743</v>
+        <v>0.0412</v>
       </c>
       <c r="L15" t="n">
-        <v>0.515</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6002</v>
+        <v>-0.0056</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6214</v>
+        <v>0.2669</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9788</v>
+        <v>-0.2725</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4495</v>
+        <v>0.4489</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0532</v>
+        <v>0.3126</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6037</v>
+        <v>0.1363</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ROPERO MORA</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7658</v>
+        <v>1.0242</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1347</v>
+        <v>2.4321</v>
       </c>
       <c r="F16" t="n">
-        <v>0.631</v>
+        <v>-1.4079</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1168</v>
+        <v>-0.2109</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3081</v>
+        <v>0.2529</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1913</v>
+        <v>-0.4638</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1224</v>
+        <v>2.3894</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0412</v>
+        <v>1.8743</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0056</v>
+        <v>-2.6002</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2669</v>
+        <v>-1.6214</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2725</v>
+        <v>-0.9788</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0668</v>
+        <v>-0.3306</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0123</v>
+        <v>-0.5527</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0545</v>
+        <v>0.2221</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7924</v>
+        <v>-0.6556</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0036</v>
+        <v>-0.7033</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2112</v>
+        <v>0.0476</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0624</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3878</v>
+        <v>0.5246</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5204</v>
+        <v>-0.2201</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9083</v>
+        <v>0.7447</v>
       </c>
       <c r="V17" t="n">
         <v>-0.894</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0068</v>
+        <v>-1.2982</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9895</v>
+        <v>-1.3899</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0173</v>
+        <v>0.0917</v>
       </c>
       <c r="G18" t="n">
         <v>-1.25</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0491</v>
+        <v>-0.2423</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2434</v>
+        <v>-0.157</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1943</v>
+        <v>-0.0852</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7409</v>
+        <v>-2.2876</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1096</v>
+        <v>-1.1897</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6313</v>
+        <v>-1.0979</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1437</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1977</v>
+        <v>0.3065</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3415</v>
+        <v>-1.1256</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0235</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0577</v>
+        <v>0.3295</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08119999999999999</v>
+        <v>-1.2535</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1673</v>
+        <v>0.1048</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2554</v>
+        <v>-0.0231</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4227</v>
+        <v>0.1279</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8685</v>
+        <v>-0.2148</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4087</v>
+        <v>-0.2658</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4599</v>
+        <v>0.051</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4955</v>
+        <v>-1.8358</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1179</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1396</v>
+        <v>-2.4082</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1384</v>
+        <v>-0.9104</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.278</v>
+        <v>-1.4978</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6937</v>
+        <v>-0.1437</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1299</v>
+        <v>0.1977</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5639</v>
+        <v>-0.3415</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4266</v>
+        <v>0.0235</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1575</v>
+        <v>-0.0577</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2691</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2672</v>
+        <v>-0.1673</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9724</v>
+        <v>0.2554</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2948</v>
+        <v>-0.4227</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.194</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.1642</v>
-      </c>
       <c r="S20" t="n">
-        <v>0.4183</v>
+        <v>1.2012</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.6079</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3309</v>
+        <v>0.5933</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9418</v>
+        <v>-2.4955</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4477</v>
+        <v>-0.3776</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.506</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0122</v>
+        <v>-3.0489</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5901</v>
+        <v>-0.3621</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4221</v>
+        <v>-2.6868</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8191000000000001</v>
+        <v>-3.6937</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3065</v>
+        <v>-3.1299</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1256</v>
+        <v>-0.5639</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-1.4266</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3295</v>
+        <v>-1.1575</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2535</v>
+        <v>-0.2691</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1048</v>
+        <v>-2.2672</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0231</v>
+        <v>-1.9724</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1279</v>
+        <v>-0.2948</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9394</v>
+        <v>-0.491</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6662</v>
+        <v>-0.4131</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2732</v>
+        <v>-0.0779</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8358</v>
+        <v>0.9418</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8358</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.0291</v>
+        <v>-6.1593</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1085</v>
+        <v>-3.8082</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9206</v>
+        <v>-2.3511</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7062</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7871</v>
+        <v>0.0827</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1436</v>
+        <v>0.1567</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6435</v>
+        <v>-0.074</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7298</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.7929</v>
+        <v>-7.1278</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5239</v>
+        <v>-3.1147</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2689</v>
+        <v>-4.0131</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.8355</v>
+        <v>-3.2463</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2195</v>
+        <v>-4.1399</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.616</v>
+        <v>0.8937</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1978</v>
+        <v>-0.7185</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.277</v>
+        <v>-2.591</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9208</v>
+        <v>1.8725</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6377</v>
+        <v>-2.5277</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9425</v>
+        <v>-1.5489</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6952</v>
+        <v>-0.9788</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7463</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9105</v>
+        <v>-3.1045</v>
       </c>
       <c r="R23" t="n">
         <v>1.1642</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0128</v>
+        <v>-0.3875</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5843</v>
+        <v>-0.1857</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5715</v>
+        <v>-0.2019</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2239</v>
+        <v>-1.5537</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.425800000000001</v>
+        <v>-8.439</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1157</v>
+        <v>-6.2246</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.3101</v>
+        <v>-2.2144</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2463</v>
+        <v>-4.8355</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.1399</v>
+        <v>-2.2195</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8937</v>
+        <v>-2.616</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7185</v>
+        <v>-3.1978</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.591</v>
+        <v>-1.277</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8725</v>
+        <v>-1.9208</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5277</v>
+        <v>-1.6377</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5489</v>
+        <v>-0.9425</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9788</v>
+        <v>-0.6952</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.9403</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.1045</v>
+        <v>-2.9105</v>
       </c>
       <c r="R24" t="n">
         <v>1.1642</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6855</v>
+        <v>-0.6334</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1867</v>
+        <v>-0.1164</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4988</v>
+        <v>-0.517</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5537</v>
+        <v>-1.2239</v>
       </c>
       <c r="W24" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.5189</v>
+        <v>-25.8516</v>
       </c>
       <c r="E25" t="n">
         <v>-12.6974</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.8216</v>
+        <v>-13.1543</v>
       </c>
       <c r="G25" t="n">
         <v>-18.2448</v>
@@ -2374,7 +2374,7 @@
         <v>-10.7927</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.4522</v>
+        <v>-7.452199999999999</v>
       </c>
       <c r="J25" t="n">
         <v>-5.7399</v>
@@ -2404,16 +2404,16 @@
         <v>9.701599999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5493999999999997</v>
+        <v>1.2168</v>
       </c>
       <c r="T25" t="n">
         <v>-0.5274999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0771</v>
+        <v>1.7442</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.943200000000001</v>
+        <v>-4.9432</v>
       </c>
       <c r="W25" t="n">
         <v>7.1521</v>
